--- a/request_forms/008_parcel_recharge_user_agreement--request_forms.xlsx
+++ b/request_forms/008_parcel_recharge_user_agreement--request_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,18 +510,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Agreement</t>
+          <t>What is your name and contact information?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_page_subpage</t>
+          <t>parcel_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Subpage</t>
+          <t>Parcel Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,18 +556,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>subpage_subsubpage</t>
+          <t>consent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>subsubpage</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>subsubpage_subpage</t>
+          <t>communication_preferences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>subsubpage</t>
+          <t>Communication Preferences</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>subpage_subsubpage</t>
+          <t>recharge_options</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>subsubpage</t>
+          <t>Recharge Options</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>subpage_subpage</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>subpage</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,108 +648,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>subpage</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>User Agreement</t>
+          <t>Comments or instructions</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>subpage_subpage</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>subpage</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>first_page_subpage</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Subpage</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>subpage</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Subpage</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>User Agreement</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
